--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488126_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488126_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.869</v>
+        <v>10.1588</v>
       </c>
       <c r="E2" t="n">
-        <v>9.375299999999999</v>
+        <v>8.058999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4937</v>
+        <v>2.0998</v>
       </c>
       <c r="G2" t="n">
         <v>3.6665</v>
@@ -610,13 +610,13 @@
         <v>2.7793</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2031</v>
+        <v>1.4929</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6077</v>
+        <v>1.2914</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5954</v>
+        <v>0.2014</v>
       </c>
       <c r="V2" t="n">
         <v>3.1466</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.193</v>
+        <v>6.71</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9755</v>
+        <v>7.3447</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7825</v>
+        <v>-0.6347</v>
       </c>
       <c r="G3" t="n">
         <v>4.2289</v>
@@ -688,13 +688,13 @@
         <v>2.4087</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1853</v>
+        <v>0.7023</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1926</v>
+        <v>0.5618</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0072</v>
+        <v>0.1405</v>
       </c>
       <c r="V3" t="n">
         <v>-0.63</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1757</v>
+        <v>6.4257</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6569</v>
+        <v>5.0054</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5188</v>
+        <v>1.4203</v>
       </c>
       <c r="G4" t="n">
         <v>2.0436</v>
@@ -766,13 +766,13 @@
         <v>2.2234</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3173</v>
+        <v>0.5674</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0584</v>
+        <v>0.2901</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3758</v>
+        <v>0.2773</v>
       </c>
       <c r="V4" t="n">
         <v>2.5177</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6463</v>
+        <v>3.0437</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7556</v>
+        <v>1.7566</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8907</v>
+        <v>1.287</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3538</v>
+        <v>0.3741</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4137</v>
+        <v>1.0898</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0599</v>
+        <v>-0.7157</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1533</v>
+        <v>2.7751</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0597</v>
+        <v>1.8935</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0936</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2004</v>
+        <v>-2.401</v>
       </c>
       <c r="N5" t="n">
-        <v>0.354</v>
+        <v>-0.8037</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1536</v>
+        <v>-1.5973</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8529</v>
+        <v>2.594</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1072</v>
+        <v>0.6864</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2699</v>
+        <v>-0.092</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1627</v>
+        <v>0.7784</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2589</v>
+        <v>0.3155</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4025</v>
+        <v>2.7508</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9185</v>
+        <v>0.7124</v>
       </c>
       <c r="F6" t="n">
-        <v>1.484</v>
+        <v>2.0384</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3741</v>
+        <v>0.3538</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0898</v>
+        <v>0.4137</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7157</v>
+        <v>-0.0599</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7751</v>
+        <v>0.1533</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8935</v>
+        <v>0.0597</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.0936</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.401</v>
+        <v>0.2004</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8037</v>
+        <v>0.354</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5973</v>
+        <v>-0.1536</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>2.594</v>
+        <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0453</v>
+        <v>0.2117</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9302</v>
+        <v>0.2266</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9754</v>
+        <v>-0.0149</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3155</v>
+        <v>1.2589</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8294</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.65</v>
+        <v>-0.7912</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4794</v>
+        <v>1.5779</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2081</v>
@@ -1000,13 +1000,13 @@
         <v>2.7793</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0555</v>
+        <v>1.0129</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4303</v>
+        <v>0.2891</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6252</v>
+        <v>0.7237</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1703</v>
+        <v>0.3717</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.327</v>
+        <v>-0.0764</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4973</v>
+        <v>0.4481</v>
       </c>
       <c r="G8" t="n">
         <v>1.3557</v>
@@ -1078,13 +1078,13 @@
         <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6857</v>
+        <v>-0.4844</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2736</v>
+        <v>-0.023</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4121</v>
+        <v>-0.4614</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3144</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3765</v>
+        <v>0.193</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0613</v>
+        <v>-1.6149</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6848</v>
+        <v>1.8079</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7197</v>
@@ -1156,13 +1156,13 @@
         <v>2.2234</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9538</v>
+        <v>-0.3843</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.383</v>
+        <v>0.0634</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5708</v>
+        <v>-0.4477</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1771</v>
+        <v>-0.9812</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0332</v>
+        <v>0.1626</v>
       </c>
       <c r="F10" t="n">
         <v>-1.1439</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0547</v>
+        <v>0.1411</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0547</v>
+        <v>0.1411</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5836</v>
+        <v>-0.9895</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.186</v>
+        <v>-1.7396</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6024</v>
+        <v>0.7501</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7626</v>
@@ -1312,13 +1312,13 @@
         <v>2.0382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6004</v>
+        <v>-0.0062</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4377</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1627</v>
+        <v>-0.0149</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2589</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0755</v>
+        <v>-1.8489</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8997000000000001</v>
+        <v>1.0523</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9751</v>
+        <v>-2.9013</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5909</v>
@@ -1390,13 +1390,13 @@
         <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3549</v>
+        <v>-0.1284</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5471</v>
+        <v>-0.3945</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1922</v>
+        <v>0.2661</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9444</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>26.0735</v>
+        <v>26.6209</v>
       </c>
       <c r="E13" t="n">
-        <v>19.324</v>
+        <v>19.8709</v>
       </c>
       <c r="F13" t="n">
-        <v>6.749600000000001</v>
+        <v>6.7496</v>
       </c>
       <c r="G13" t="n">
         <v>7.933300000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>5.7448</v>
+        <v>5.744800000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1886</v>
+        <v>2.188599999999999</v>
       </c>
       <c r="J13" t="n">
         <v>17.6303</v>
@@ -1456,7 +1456,7 @@
         <v>-2.2485</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.4484</v>
+        <v>-7.448399999999999</v>
       </c>
       <c r="P13" t="n">
         <v>12.0436</v>
@@ -1468,16 +1468,16 @@
         <v>22.2344</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2642</v>
+        <v>3.811399999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8158</v>
+        <v>2.3627</v>
       </c>
       <c r="U13" t="n">
         <v>1.4485</v>
       </c>
       <c r="V13" t="n">
-        <v>2.832200000000001</v>
+        <v>2.8322</v>
       </c>
       <c r="W13" t="n">
         <v>10.0686</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3322</v>
+        <v>4.6014</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9532</v>
+        <v>5.247</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6209</v>
+        <v>-0.6456</v>
       </c>
       <c r="G14" t="n">
         <v>1.2493</v>
@@ -1546,13 +1546,13 @@
         <v>1.4823</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2674</v>
+        <v>-0.9983</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.5394</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4343</v>
+        <v>-0.4589</v>
       </c>
       <c r="V14" t="n">
         <v>4.721</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4561</v>
+        <v>-0.4012</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7738</v>
+        <v>-0.0097</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3177</v>
+        <v>-0.3915</v>
       </c>
       <c r="G15" t="n">
         <v>0.7408</v>
@@ -1624,13 +1624,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3448</v>
+        <v>0.4875</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1839</v>
+        <v>0.4004</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1609</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2589</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0508</v>
+        <v>-0.8057</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.1719</v>
+        <v>-1.9761</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1211</v>
+        <v>1.1704</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6933</v>
@@ -1702,13 +1702,13 @@
         <v>1.1117</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2283</v>
+        <v>0.0168</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.1287</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1612</v>
+        <v>-0.1119</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3144</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7413</v>
+        <v>-2.2561</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3109</v>
+        <v>1.9192</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.0522</v>
+        <v>-4.1753</v>
       </c>
       <c r="G17" t="n">
         <v>0.029</v>
@@ -1780,13 +1780,13 @@
         <v>0.3706</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3768</v>
+        <v>-0.138</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5646</v>
+        <v>0.1729</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1878</v>
+        <v>-0.3109</v>
       </c>
       <c r="V17" t="n">
         <v>-2.5177</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2057</v>
+        <v>-2.3517</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4356</v>
+        <v>-1.7294</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.77</v>
+        <v>-0.6223</v>
       </c>
       <c r="G18" t="n">
         <v>-4.5147</v>
@@ -1858,13 +1858,13 @@
         <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5325</v>
+        <v>0.3864</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2363</v>
+        <v>-0.0575</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2962</v>
+        <v>0.4439</v>
       </c>
       <c r="V18" t="n">
         <v>2.5177</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.231</v>
+        <v>-2.9619</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3203</v>
+        <v>-2.0266</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9107</v>
+        <v>-0.9353</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5783</v>
@@ -1936,13 +1936,13 @@
         <v>0.7411</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6146</v>
+        <v>-0.3454</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0124</v>
+        <v>0.2814</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6021</v>
+        <v>-0.6268</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.7831</v>
+        <v>-4.3897</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0187</v>
+        <v>-2.9208</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7644</v>
+        <v>-1.4689</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8532</v>
@@ -2014,13 +2014,13 @@
         <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1125</v>
+        <v>-0.7191</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.909</v>
+        <v>-0.8111</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2035</v>
+        <v>0.092</v>
       </c>
       <c r="V20" t="n">
         <v>1.2589</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8643</v>
+        <v>-4.9639</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5571</v>
+        <v>0.7529</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.4213</v>
+        <v>-5.7168</v>
       </c>
       <c r="G21" t="n">
         <v>0.0701</v>
@@ -2092,13 +2092,13 @@
         <v>0.9264</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5638</v>
+        <v>-0.6634</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7449</v>
+        <v>-0.549</v>
       </c>
       <c r="U21" t="n">
-        <v>0.181</v>
+        <v>-0.1144</v>
       </c>
       <c r="V21" t="n">
         <v>-2.5177</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3488</v>
+        <v>-5.9565</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7823</v>
+        <v>-3.4885</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5665</v>
+        <v>-2.468</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3754</v>
@@ -2170,13 +2170,13 @@
         <v>1.297</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1766</v>
+        <v>-0.7844</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2649</v>
+        <v>0.0289</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9118000000000001</v>
+        <v>-0.8133</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3144</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.637</v>
+        <v>-6.5883</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6156</v>
+        <v>-2.5177</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.0214</v>
+        <v>-4.0706</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0077</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5551</v>
+        <v>-0.5064</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6019</v>
+        <v>-0.5039</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0467</v>
+        <v>-0.0025</v>
       </c>
       <c r="V23" t="n">
         <v>-4.4065</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-26.0737</v>
+        <v>-26.0736</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.7494</v>
+        <v>-6.749699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-19.324</v>
+        <v>-19.3239</v>
       </c>
       <c r="G24" t="n">
         <v>-7.9334</v>
@@ -2326,13 +2326,13 @@
         <v>10.1907</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.2642</v>
+        <v>-3.2643</v>
       </c>
       <c r="T24" t="n">
         <v>-1.4486</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.8159</v>
+        <v>-1.8158</v>
       </c>
       <c r="V24" t="n">
         <v>-2.832</v>
